--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/2_fold/142.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/2_fold/142.xlsx
@@ -426,13 +426,13 @@
         <v>-12.05449509476226</v>
       </c>
       <c r="E2">
-        <v>-21.97002543021483</v>
+        <v>-19.49701235969097</v>
       </c>
       <c r="F2">
-        <v>0.5619800377923301</v>
+        <v>-0.5369454126399389</v>
       </c>
       <c r="G2">
-        <v>-12.98505721790648</v>
+        <v>-11.49741839946585</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-11.94472345025412</v>
       </c>
       <c r="E3">
-        <v>-23.5118013042743</v>
+        <v>-19.54259385398096</v>
       </c>
       <c r="F3">
-        <v>0.8436199845397452</v>
+        <v>-0.3842922109172404</v>
       </c>
       <c r="G3">
-        <v>-12.77400593053317</v>
+        <v>-11.55697992656751</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-11.77931358932582</v>
       </c>
       <c r="E4">
-        <v>-22.12169655458624</v>
+        <v>-19.14036364359397</v>
       </c>
       <c r="F4">
-        <v>1.134209612707006</v>
+        <v>-0.3941878879110833</v>
       </c>
       <c r="G4">
-        <v>-12.2205750706198</v>
+        <v>-10.8764410501189</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-11.58206425438148</v>
       </c>
       <c r="E5">
-        <v>-24.00224572320066</v>
+        <v>-21.00608584777875</v>
       </c>
       <c r="F5">
-        <v>0.7394196489415954</v>
+        <v>-0.6668118838464285</v>
       </c>
       <c r="G5">
-        <v>-11.84323632263242</v>
+        <v>-10.91332434432985</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-11.35435338875001</v>
       </c>
       <c r="E6">
-        <v>-21.53454045674993</v>
+        <v>-20.32777922099642</v>
       </c>
       <c r="F6">
-        <v>1.411926411434763</v>
+        <v>-0.5635177821869415</v>
       </c>
       <c r="G6">
-        <v>-10.88739573442321</v>
+        <v>-10.83094099338497</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-11.11926877479688</v>
       </c>
       <c r="E7">
-        <v>-23.98210264827524</v>
+        <v>-21.71297072168721</v>
       </c>
       <c r="F7">
-        <v>1.349232252921285</v>
+        <v>-0.6380145194555066</v>
       </c>
       <c r="G7">
-        <v>-11.36907811148361</v>
+        <v>-10.8916864931587</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-10.87908564352764</v>
       </c>
       <c r="E8">
-        <v>-25.14720302122939</v>
+        <v>-21.76834133506983</v>
       </c>
       <c r="F8">
-        <v>0.9934467966840917</v>
+        <v>-0.4859469734865873</v>
       </c>
       <c r="G8">
-        <v>-12.20908257292972</v>
+        <v>-10.67181349981203</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-10.64642277019462</v>
       </c>
       <c r="E9">
-        <v>-25.80103062046317</v>
+        <v>-22.67538607556708</v>
       </c>
       <c r="F9">
-        <v>0.9981602072060209</v>
+        <v>-0.2997332948068697</v>
       </c>
       <c r="G9">
-        <v>-10.86668991907109</v>
+        <v>-9.96816692298747</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-10.42383746907505</v>
       </c>
       <c r="E10">
-        <v>-24.97813409461827</v>
+        <v>-23.18453240508914</v>
       </c>
       <c r="F10">
-        <v>0.8647267859630766</v>
+        <v>-0.02148882604352973</v>
       </c>
       <c r="G10">
-        <v>-11.33554570795535</v>
+        <v>-9.927940570327596</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-10.21150960326926</v>
       </c>
       <c r="E11">
-        <v>-24.64263768379862</v>
+        <v>-24.61842030856354</v>
       </c>
       <c r="F11">
-        <v>1.259501839115237</v>
+        <v>0.04346429037738231</v>
       </c>
       <c r="G11">
-        <v>-10.58279755223343</v>
+        <v>-9.584036322946311</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-10.01803774577135</v>
       </c>
       <c r="E12">
-        <v>-25.5937646092976</v>
+        <v>-24.2833101463971</v>
       </c>
       <c r="F12">
-        <v>1.27085047253359</v>
+        <v>0.3143503715016542</v>
       </c>
       <c r="G12">
-        <v>-9.781049636653197</v>
+        <v>-8.967305349676803</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-9.838959158944823</v>
       </c>
       <c r="E13">
-        <v>-27.6104394322946</v>
+        <v>-24.97588720729154</v>
       </c>
       <c r="F13">
-        <v>1.980307391396032</v>
+        <v>-0.03823592982592734</v>
       </c>
       <c r="G13">
-        <v>-9.918120254548123</v>
+        <v>-8.958841315712412</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-9.693296773805976</v>
       </c>
       <c r="E14">
-        <v>-26.7703818372555</v>
+        <v>-25.08064780974901</v>
       </c>
       <c r="F14">
-        <v>1.61113883139921</v>
+        <v>0.2596623839362337</v>
       </c>
       <c r="G14">
-        <v>-10.62795690679821</v>
+        <v>-8.173204305003944</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-9.576904648162813</v>
       </c>
       <c r="E15">
-        <v>-28.75563761658017</v>
+        <v>-26.40620750223791</v>
       </c>
       <c r="F15">
-        <v>2.124981758294966</v>
+        <v>0.6267194354233198</v>
       </c>
       <c r="G15">
-        <v>-10.28010390822287</v>
+        <v>-7.982067777371653</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-9.507231922351878</v>
       </c>
       <c r="E16">
-        <v>-30.78210571188111</v>
+        <v>-26.78544553473066</v>
       </c>
       <c r="F16">
-        <v>2.095949137561649</v>
+        <v>0.816484325158839</v>
       </c>
       <c r="G16">
-        <v>-9.994706447128431</v>
+        <v>-8.179022349325239</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-9.472798104777684</v>
       </c>
       <c r="E17">
-        <v>-28.09526455629846</v>
+        <v>-27.37886467524481</v>
       </c>
       <c r="F17">
-        <v>1.828229076650877</v>
+        <v>1.017767663630285</v>
       </c>
       <c r="G17">
-        <v>-8.471731200647087</v>
+        <v>-7.539700603108827</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-9.480094003950331</v>
       </c>
       <c r="E18">
-        <v>-30.89500868514091</v>
+        <v>-28.31512725741223</v>
       </c>
       <c r="F18">
-        <v>2.316448943043238</v>
+        <v>1.160157393232298</v>
       </c>
       <c r="G18">
-        <v>-8.630798647094437</v>
+        <v>-7.732386607655942</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-9.507830346258734</v>
       </c>
       <c r="E19">
-        <v>-30.15204071124233</v>
+        <v>-28.77465932444789</v>
       </c>
       <c r="F19">
-        <v>2.564435635684521</v>
+        <v>1.066883223677074</v>
       </c>
       <c r="G19">
-        <v>-7.674334090927948</v>
+        <v>-6.983024587668696</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-9.553168268973923</v>
       </c>
       <c r="E20">
-        <v>-32.04627678777772</v>
+        <v>-29.06213630592987</v>
       </c>
       <c r="F20">
-        <v>3.13841803602352</v>
+        <v>1.372787708387292</v>
       </c>
       <c r="G20">
-        <v>-7.878630076671745</v>
+        <v>-6.401815405305874</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-9.592218308465718</v>
       </c>
       <c r="E21">
-        <v>-32.090091090649</v>
+        <v>-30.15881252230747</v>
       </c>
       <c r="F21">
-        <v>2.347436510847162</v>
+        <v>1.543411512546323</v>
       </c>
       <c r="G21">
-        <v>-6.942994040853156</v>
+        <v>-6.847315473078036</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-9.619723616790104</v>
       </c>
       <c r="E22">
-        <v>-31.49888561177098</v>
+        <v>-30.05890287067739</v>
       </c>
       <c r="F22">
-        <v>3.568493137678579</v>
+        <v>1.784229513683778</v>
       </c>
       <c r="G22">
-        <v>-8.220851699164056</v>
+        <v>-6.749772833664862</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-9.619598082671983</v>
       </c>
       <c r="E23">
-        <v>-33.01934720531143</v>
+        <v>-30.42441661634724</v>
       </c>
       <c r="F23">
-        <v>4.176595991338891</v>
+        <v>1.99323157961451</v>
       </c>
       <c r="G23">
-        <v>-7.785964308154769</v>
+        <v>-6.285590277598693</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-9.588078383591018</v>
       </c>
       <c r="E24">
-        <v>-32.14850808453838</v>
+        <v>-30.69046095078744</v>
       </c>
       <c r="F24">
-        <v>3.230873778584779</v>
+        <v>1.883312195467433</v>
       </c>
       <c r="G24">
-        <v>-7.204494051332836</v>
+        <v>-6.296202954361569</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-9.523347242408844</v>
       </c>
       <c r="E25">
-        <v>-35.52565241781512</v>
+        <v>-31.21792501885766</v>
       </c>
       <c r="F25">
-        <v>4.023614756124683</v>
+        <v>1.959260232425702</v>
       </c>
       <c r="G25">
-        <v>-7.52439641831572</v>
+        <v>-6.287673651782401</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-9.423526591215857</v>
       </c>
       <c r="E26">
-        <v>-33.74805512812622</v>
+        <v>-31.35905321628099</v>
       </c>
       <c r="F26">
-        <v>3.381171103413915</v>
+        <v>1.851203018200118</v>
       </c>
       <c r="G26">
-        <v>-7.979417871611673</v>
+        <v>-6.329954660435481</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-9.298492447848355</v>
       </c>
       <c r="E27">
-        <v>-34.85616098206975</v>
+        <v>-31.51133486271716</v>
       </c>
       <c r="F27">
-        <v>2.929705898683768</v>
+        <v>1.977920036541164</v>
       </c>
       <c r="G27">
-        <v>-8.274553410030961</v>
+        <v>-5.887034008319339</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-9.14508121929649</v>
       </c>
       <c r="E28">
-        <v>-34.21166357207719</v>
+        <v>-30.95273001613338</v>
       </c>
       <c r="F28">
-        <v>3.625496412134824</v>
+        <v>1.974792121228193</v>
       </c>
       <c r="G28">
-        <v>-7.13192318393366</v>
+        <v>-6.24770837358164</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-8.976978062326836</v>
       </c>
       <c r="E29">
-        <v>-35.01835219072695</v>
+        <v>-31.7285914237246</v>
       </c>
       <c r="F29">
-        <v>3.539460516945262</v>
+        <v>1.877811835912844</v>
       </c>
       <c r="G29">
-        <v>-7.530730084693761</v>
+        <v>-6.597334067734348</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-8.787427017645948</v>
       </c>
       <c r="E30">
-        <v>-33.45231117950216</v>
+        <v>-31.26390522143483</v>
       </c>
       <c r="F30">
-        <v>3.228584171083441</v>
+        <v>1.874574576102704</v>
       </c>
       <c r="G30">
-        <v>-8.020076302501376</v>
+        <v>-6.378383972600632</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-8.585748865920335</v>
       </c>
       <c r="E31">
-        <v>-33.70479320236114</v>
+        <v>-31.26874786583958</v>
       </c>
       <c r="F31">
-        <v>3.529503540763612</v>
+        <v>2.043942575279091</v>
       </c>
       <c r="G31">
-        <v>-8.318159371564031</v>
+        <v>-6.442686611879753</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-8.361483410676804</v>
       </c>
       <c r="E32">
-        <v>-31.30526912962446</v>
+        <v>-30.66293138952082</v>
       </c>
       <c r="F32">
-        <v>3.470861755584629</v>
+        <v>2.037579056890785</v>
       </c>
       <c r="G32">
-        <v>-7.557845278017064</v>
+        <v>-6.46866352056133</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-8.121197045322941</v>
       </c>
       <c r="E33">
-        <v>-34.48285788856018</v>
+        <v>-30.54162854635655</v>
       </c>
       <c r="F33">
-        <v>3.735553305270766</v>
+        <v>1.83295242758164</v>
       </c>
       <c r="G33">
-        <v>-8.029877037696416</v>
+        <v>-6.266033189866664</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-7.856134015374741</v>
       </c>
       <c r="E34">
-        <v>-33.27455581140516</v>
+        <v>-30.75683757418085</v>
       </c>
       <c r="F34">
-        <v>3.525191060064638</v>
+        <v>1.881367188805659</v>
       </c>
       <c r="G34">
-        <v>-7.513984768886361</v>
+        <v>-6.23652394375331</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-7.574131310423143</v>
       </c>
       <c r="E35">
-        <v>-33.23270597749053</v>
+        <v>-29.20382518688205</v>
       </c>
       <c r="F35">
-        <v>3.311934499153127</v>
+        <v>1.963947135190742</v>
       </c>
       <c r="G35">
-        <v>-7.647422535682752</v>
+        <v>-6.64376877103189</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-7.273067714966677</v>
       </c>
       <c r="E36">
-        <v>-31.66698891674908</v>
+        <v>-28.70863987722841</v>
       </c>
       <c r="F36">
-        <v>3.234280025345091</v>
+        <v>1.613796234027391</v>
       </c>
       <c r="G36">
-        <v>-7.363224711727933</v>
+        <v>-6.311402709371031</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-6.962970770984239</v>
       </c>
       <c r="E37">
-        <v>-30.22449763601529</v>
+        <v>-29.3344997514008</v>
       </c>
       <c r="F37">
-        <v>3.03611134830817</v>
+        <v>1.641258270165</v>
       </c>
       <c r="G37">
-        <v>-7.450131177676912</v>
+        <v>-6.255634594160259</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-6.650344363063041</v>
       </c>
       <c r="E38">
-        <v>-31.40478630278434</v>
+        <v>-28.50973428045972</v>
       </c>
       <c r="F38">
-        <v>3.297870477388397</v>
+        <v>1.690811208200467</v>
       </c>
       <c r="G38">
-        <v>-7.197661732737893</v>
+        <v>-6.361455904671854</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-6.343255076448993</v>
       </c>
       <c r="E39">
-        <v>-32.28891569979685</v>
+        <v>-27.83898234507726</v>
       </c>
       <c r="F39">
-        <v>2.922722761478168</v>
+        <v>1.673480105399096</v>
       </c>
       <c r="G39">
-        <v>-6.832985096017416</v>
+        <v>-5.706279106553611</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-6.052689970547388</v>
       </c>
       <c r="E40">
-        <v>-29.97977173530543</v>
+        <v>-27.17482570927863</v>
       </c>
       <c r="F40">
-        <v>2.680639014949235</v>
+        <v>1.756500743242468</v>
       </c>
       <c r="G40">
-        <v>-7.818300990660298</v>
+        <v>-5.924451199799175</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-5.781319909895648</v>
       </c>
       <c r="E41">
-        <v>-30.45789149962536</v>
+        <v>-27.02127733338839</v>
       </c>
       <c r="F41">
-        <v>3.441350338492494</v>
+        <v>1.447317580351969</v>
       </c>
       <c r="G41">
-        <v>-7.755768436213954</v>
+        <v>-6.057037863858863</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-5.542303846708495</v>
       </c>
       <c r="E42">
-        <v>-29.42765212820538</v>
+        <v>-26.12226075038203</v>
       </c>
       <c r="F42">
-        <v>2.961470475111518</v>
+        <v>1.496144868542583</v>
       </c>
       <c r="G42">
-        <v>-6.712144171873146</v>
+        <v>-5.763668494155463</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-5.33336059039133</v>
       </c>
       <c r="E43">
-        <v>-30.76173421033283</v>
+        <v>-25.51288081874657</v>
       </c>
       <c r="F43">
-        <v>3.271013149454832</v>
+        <v>1.782196700077308</v>
       </c>
       <c r="G43">
-        <v>-7.538131545609567</v>
+        <v>-6.042963339768171</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-5.165788878307313</v>
       </c>
       <c r="E44">
-        <v>-30.53853855713088</v>
+        <v>-25.87384056819874</v>
       </c>
       <c r="F44">
-        <v>2.780394331063963</v>
+        <v>1.61939434093551</v>
       </c>
       <c r="G44">
-        <v>-6.790205435147433</v>
+        <v>-5.666232895270523</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-5.033053937597853</v>
       </c>
       <c r="E45">
-        <v>-28.97020289664912</v>
+        <v>-25.3267421935904</v>
       </c>
       <c r="F45">
-        <v>2.735924255412074</v>
+        <v>1.611287937531714</v>
       </c>
       <c r="G45">
-        <v>-7.564609717252639</v>
+        <v>-5.520464581770304</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-4.942249641692732</v>
       </c>
       <c r="E46">
-        <v>-28.30906772208931</v>
+        <v>-25.94830764725291</v>
       </c>
       <c r="F46">
-        <v>3.314010387864543</v>
+        <v>1.293816130408804</v>
       </c>
       <c r="G46">
-        <v>-7.229332675372688</v>
+        <v>-5.839766477497233</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-4.884241744988449</v>
       </c>
       <c r="E47">
-        <v>-28.17657820422161</v>
+        <v>-24.29454042981944</v>
       </c>
       <c r="F47">
-        <v>3.160339950971207</v>
+        <v>1.790491971248942</v>
       </c>
       <c r="G47">
-        <v>-6.670017197150942</v>
+        <v>-5.653064299552948</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-4.862642659303757</v>
       </c>
       <c r="E48">
-        <v>-26.96839034037803</v>
+        <v>-23.98440352734919</v>
       </c>
       <c r="F48">
-        <v>2.964583479811238</v>
+        <v>1.457269586329202</v>
       </c>
       <c r="G48">
-        <v>-6.387696498557133</v>
+        <v>-5.301483157701496</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-4.86703708110254</v>
       </c>
       <c r="E49">
-        <v>-26.87785863991941</v>
+        <v>-23.94878558702746</v>
       </c>
       <c r="F49">
-        <v>3.090159007871227</v>
+        <v>1.841839153078873</v>
       </c>
       <c r="G49">
-        <v>-6.298463859177473</v>
+        <v>-5.548950416003942</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-4.899017214007836</v>
       </c>
       <c r="E50">
-        <v>-26.85789830629229</v>
+        <v>-23.73181352099577</v>
       </c>
       <c r="F50">
-        <v>3.118769161229116</v>
+        <v>1.302823797546846</v>
       </c>
       <c r="G50">
-        <v>-6.620512258214252</v>
+        <v>-6.019129852395897</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-4.949255005978666</v>
       </c>
       <c r="E51">
-        <v>-26.62413896008564</v>
+        <v>-22.69581156886259</v>
       </c>
       <c r="F51">
-        <v>3.302998071611726</v>
+        <v>1.339611593905172</v>
       </c>
       <c r="G51">
-        <v>-6.281757704538939</v>
+        <v>-6.155374169627736</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-5.017690235255764</v>
       </c>
       <c r="E52">
-        <v>-25.79816905786036</v>
+        <v>-23.11217515738797</v>
       </c>
       <c r="F52">
-        <v>3.137690729443862</v>
+        <v>1.472700414308551</v>
       </c>
       <c r="G52">
-        <v>-7.216286784650895</v>
+        <v>-6.181090003850201</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-5.098671364170326</v>
       </c>
       <c r="E53">
-        <v>-24.08106536772325</v>
+        <v>-22.19836068243125</v>
       </c>
       <c r="F53">
-        <v>3.68096720689589</v>
+        <v>1.262815308726435</v>
       </c>
       <c r="G53">
-        <v>-6.836081439102476</v>
+        <v>-5.750818409278003</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-5.189145868273237</v>
       </c>
       <c r="E54">
-        <v>-26.12928798394364</v>
+        <v>-21.79903771997164</v>
       </c>
       <c r="F54">
-        <v>2.29564201061972</v>
+        <v>1.653945545306277</v>
       </c>
       <c r="G54">
-        <v>-6.95106907387347</v>
+        <v>-5.908922490971233</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-5.28760471820544</v>
       </c>
       <c r="E55">
-        <v>-24.3075150619982</v>
+        <v>-21.53909652957327</v>
       </c>
       <c r="F55">
-        <v>2.499282882719534</v>
+        <v>1.416310131730378</v>
       </c>
       <c r="G55">
-        <v>-7.327071120630196</v>
+        <v>-6.057740154153872</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-5.38778568253538</v>
       </c>
       <c r="E56">
-        <v>-24.17746970899517</v>
+        <v>-21.6188589530666</v>
       </c>
       <c r="F56">
-        <v>2.950825953985544</v>
+        <v>1.135826585877271</v>
       </c>
       <c r="G56">
-        <v>-6.690903153879849</v>
+        <v>-6.463559514885704</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-5.491850046537576</v>
       </c>
       <c r="E57">
-        <v>-25.23201990290504</v>
+        <v>-20.57592529123228</v>
       </c>
       <c r="F57">
-        <v>2.385282960746266</v>
+        <v>1.255527332316605</v>
       </c>
       <c r="G57">
-        <v>-7.19859376855692</v>
+        <v>-6.603678177090754</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-5.592285044501588</v>
       </c>
       <c r="E58">
-        <v>-24.42931213731012</v>
+        <v>-21.02082144155924</v>
       </c>
       <c r="F58">
-        <v>2.386527168585271</v>
+        <v>1.256557821365688</v>
       </c>
       <c r="G58">
-        <v>-6.821273295781682</v>
+        <v>-6.329988600115166</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-5.692155307817792</v>
       </c>
       <c r="E59">
-        <v>-25.35709801516357</v>
+        <v>-21.2869010782957</v>
       </c>
       <c r="F59">
-        <v>2.398366195506081</v>
+        <v>1.35220443516253</v>
       </c>
       <c r="G59">
-        <v>-7.645159020122256</v>
+        <v>-6.690558535593822</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-5.782409371921343</v>
       </c>
       <c r="E60">
-        <v>-22.3447863008994</v>
+        <v>-20.35384062205972</v>
       </c>
       <c r="F60">
-        <v>2.997086959962286</v>
+        <v>1.337510854171672</v>
       </c>
       <c r="G60">
-        <v>-7.020540987442994</v>
+        <v>-6.255250814705366</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-5.864933061895073</v>
       </c>
       <c r="E61">
-        <v>-23.95032227521765</v>
+        <v>-20.71667346981939</v>
       </c>
       <c r="F61">
-        <v>2.855081592835172</v>
+        <v>1.204998577480641</v>
       </c>
       <c r="G61">
-        <v>-6.79122884702715</v>
+        <v>-6.484544679909072</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-5.928635985682832</v>
       </c>
       <c r="E62">
-        <v>-24.70157590570926</v>
+        <v>-19.88426609004063</v>
       </c>
       <c r="F62">
-        <v>1.886029240548615</v>
+        <v>1.199110541981542</v>
       </c>
       <c r="G62">
-        <v>-8.094024337672364</v>
+        <v>-7.185252863696332</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-5.973985655569302</v>
       </c>
       <c r="E63">
-        <v>-23.1447654066539</v>
+        <v>-19.55061785826053</v>
       </c>
       <c r="F63">
-        <v>2.051419419456759</v>
+        <v>1.129496202185077</v>
       </c>
       <c r="G63">
-        <v>-8.139968220986775</v>
+        <v>-6.894551674965049</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-5.991626560409625</v>
       </c>
       <c r="E64">
-        <v>-22.7881831419381</v>
+        <v>-19.76157192108255</v>
       </c>
       <c r="F64">
-        <v>2.741961397043677</v>
+        <v>1.370352308223061</v>
       </c>
       <c r="G64">
-        <v>-8.38943661501831</v>
+        <v>-6.975424710163965</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-5.983941890207105</v>
       </c>
       <c r="E65">
-        <v>-22.53207121238122</v>
+        <v>-19.92995556782507</v>
       </c>
       <c r="F65">
-        <v>2.468326792876916</v>
+        <v>0.8389496491227616</v>
       </c>
       <c r="G65">
-        <v>-7.786502121540539</v>
+        <v>-7.158312590260634</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-5.946093075350936</v>
       </c>
       <c r="E66">
-        <v>-22.71780697603888</v>
+        <v>-20.26101634894981</v>
       </c>
       <c r="F66">
-        <v>2.256312783069605</v>
+        <v>0.890200740333967</v>
       </c>
       <c r="G66">
-        <v>-6.933668461173699</v>
+        <v>-7.333446558921695</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-5.881236842130128</v>
       </c>
       <c r="E67">
-        <v>-23.47477957852478</v>
+        <v>-19.85803856052434</v>
       </c>
       <c r="F67">
-        <v>2.579917822442843</v>
+        <v>0.9933904677007014</v>
       </c>
       <c r="G67">
-        <v>-8.868420787543796</v>
+        <v>-7.324269791683932</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-5.792767668237712</v>
       </c>
       <c r="E68">
-        <v>-21.55703009607388</v>
+        <v>-19.45225735445462</v>
       </c>
       <c r="F68">
-        <v>1.768495503235004</v>
+        <v>0.9372752031002572</v>
       </c>
       <c r="G68">
-        <v>-7.910162649843211</v>
+        <v>-7.309064815185288</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-5.684859466126339</v>
       </c>
       <c r="E69">
-        <v>-21.34499204509608</v>
+        <v>-19.56694413197843</v>
       </c>
       <c r="F69">
-        <v>2.63893071621828</v>
+        <v>0.6303576250564152</v>
       </c>
       <c r="G69">
-        <v>-8.530371134908084</v>
+        <v>-7.725853219316682</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-5.565714881524131</v>
       </c>
       <c r="E70">
-        <v>-22.17109485008375</v>
+        <v>-19.75457376000021</v>
       </c>
       <c r="F70">
-        <v>2.218857322584623</v>
+        <v>0.8682026155852233</v>
       </c>
       <c r="G70">
-        <v>-8.721857502315583</v>
+        <v>-6.519849779014697</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-5.434122920470911</v>
       </c>
       <c r="E71">
-        <v>-24.11028736260474</v>
+        <v>-19.6548593093024</v>
       </c>
       <c r="F71">
-        <v>2.017022291422912</v>
+        <v>0.5249354475391361</v>
       </c>
       <c r="G71">
-        <v>-8.484714433498693</v>
+        <v>-7.156962835307028</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-5.298114820000661</v>
       </c>
       <c r="E72">
-        <v>-24.28235906100372</v>
+        <v>-19.62563316120958</v>
       </c>
       <c r="F72">
-        <v>1.369818839615658</v>
+        <v>0.4662928339927507</v>
       </c>
       <c r="G72">
-        <v>-8.279384592896816</v>
+        <v>-7.27963911289885</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-5.153854555524084</v>
       </c>
       <c r="E73">
-        <v>-24.82592720598595</v>
+        <v>-19.95172670158982</v>
       </c>
       <c r="F73">
-        <v>1.602354823459924</v>
+        <v>0.470249945075924</v>
       </c>
       <c r="G73">
-        <v>-7.249597274888909</v>
+        <v>-7.224991007117667</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-5.008933811281124</v>
       </c>
       <c r="E74">
-        <v>-23.90711641780546</v>
+        <v>-19.93898880245657</v>
       </c>
       <c r="F74">
-        <v>1.547086150345141</v>
+        <v>0.3077689924864122</v>
       </c>
       <c r="G74">
-        <v>-7.931378865762893</v>
+        <v>-7.518611008301813</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-4.859556305172863</v>
       </c>
       <c r="E75">
-        <v>-22.54169004980952</v>
+        <v>-19.82423972676289</v>
       </c>
       <c r="F75">
-        <v>1.677643479965566</v>
+        <v>0.1936448154027243</v>
       </c>
       <c r="G75">
-        <v>-7.498351630274774</v>
+        <v>-6.815480053534001</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-4.713356984782371</v>
       </c>
       <c r="E76">
-        <v>-24.38666696342678</v>
+        <v>-20.18865079482599</v>
       </c>
       <c r="F76">
-        <v>1.196095284635352</v>
+        <v>0.2272500241994946</v>
       </c>
       <c r="G76">
-        <v>-8.207839748121948</v>
+        <v>-6.68441023208175</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-4.567612998629052</v>
       </c>
       <c r="E77">
-        <v>-23.19927630529228</v>
+        <v>-20.45050661564511</v>
       </c>
       <c r="F77">
-        <v>1.346697448668718</v>
+        <v>0.0887080611834857</v>
       </c>
       <c r="G77">
-        <v>-8.603898840199902</v>
+        <v>-6.42647649871353</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-4.429406369836246</v>
       </c>
       <c r="E78">
-        <v>-24.16258459960698</v>
+        <v>-21.42935622673732</v>
       </c>
       <c r="F78">
-        <v>1.148218962223151</v>
+        <v>-0.08945057287140956</v>
       </c>
       <c r="G78">
-        <v>-7.305031214792018</v>
+        <v>-6.167963180046084</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-4.297054621223252</v>
       </c>
       <c r="E79">
-        <v>-23.85133048329036</v>
+        <v>-21.68018942470034</v>
       </c>
       <c r="F79">
-        <v>1.11094739930159</v>
+        <v>-0.1084864557877422</v>
       </c>
       <c r="G79">
-        <v>-7.066672844367966</v>
+        <v>-6.047597411417397</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-4.175400282005682</v>
       </c>
       <c r="E80">
-        <v>-24.71269405242582</v>
+        <v>-21.00424182195052</v>
       </c>
       <c r="F80">
-        <v>1.213505910707392</v>
+        <v>-0.131587137549612</v>
       </c>
       <c r="G80">
-        <v>-6.463828421578588</v>
+        <v>-5.900763914124004</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-4.064049618621032</v>
       </c>
       <c r="E81">
-        <v>-23.39603469180603</v>
+        <v>-22.37314027461401</v>
       </c>
       <c r="F81">
-        <v>0.5403927832753749</v>
+        <v>-0.2365769072826298</v>
       </c>
       <c r="G81">
-        <v>-6.246275074801118</v>
+        <v>-5.594870802617034</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-3.963181703996338</v>
       </c>
       <c r="E82">
-        <v>-23.49627660034209</v>
+        <v>-23.04368454943023</v>
       </c>
       <c r="F82">
-        <v>0.3304993940192306</v>
+        <v>-0.3065880350650356</v>
       </c>
       <c r="G82">
-        <v>-5.966408476122957</v>
+        <v>-4.932266436137072</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-3.87251242021081</v>
       </c>
       <c r="E83">
-        <v>-26.68024884508407</v>
+        <v>-23.67356888537637</v>
       </c>
       <c r="F83">
-        <v>1.278118568125753</v>
+        <v>-0.5018980161948946</v>
       </c>
       <c r="G83">
-        <v>-6.259373180414734</v>
+        <v>-5.21812469365184</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-3.787022002541767</v>
       </c>
       <c r="E84">
-        <v>-25.26410761360066</v>
+        <v>-24.13096204857974</v>
       </c>
       <c r="F84">
-        <v>1.021212015291125</v>
+        <v>-0.3105227802283332</v>
       </c>
       <c r="G84">
-        <v>-6.687148903157827</v>
+        <v>-5.132406116491817</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-3.707570540815335</v>
       </c>
       <c r="E85">
-        <v>-27.77870678912003</v>
+        <v>-24.84711689016522</v>
       </c>
       <c r="F85">
-        <v>1.628695250134143</v>
+        <v>-0.2991261015006176</v>
       </c>
       <c r="G85">
-        <v>-6.697088007816196</v>
+        <v>-4.660033654643326</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-3.627287032957412</v>
       </c>
       <c r="E86">
-        <v>-27.90322837106103</v>
+        <v>-25.90826238365892</v>
       </c>
       <c r="F86">
-        <v>0.3173846812981088</v>
+        <v>-0.4092144725978663</v>
       </c>
       <c r="G86">
-        <v>-5.620607522796228</v>
+        <v>-4.704938461610475</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-3.547891005007989</v>
       </c>
       <c r="E87">
-        <v>-29.26193068992207</v>
+        <v>-27.08485469234887</v>
       </c>
       <c r="F87">
-        <v>0.1633307102972764</v>
+        <v>-0.5987233968059205</v>
       </c>
       <c r="G87">
-        <v>-5.625285977103503</v>
+        <v>-4.243857470118548</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-3.462061284589494</v>
       </c>
       <c r="E88">
-        <v>-30.58357390413165</v>
+        <v>-27.72857337521802</v>
       </c>
       <c r="F88">
-        <v>0.2310572007827612</v>
+        <v>-0.7310318951158631</v>
       </c>
       <c r="G88">
-        <v>-5.569058370844696</v>
+        <v>-4.301254689954174</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-3.37072461893139</v>
       </c>
       <c r="E89">
-        <v>-30.25102004353565</v>
+        <v>-28.64860313092235</v>
       </c>
       <c r="F89">
-        <v>0.3590838679876331</v>
+        <v>-0.7065072497885809</v>
       </c>
       <c r="G89">
-        <v>-5.642885006392198</v>
+        <v>-4.040172398609072</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-3.267125707582434</v>
       </c>
       <c r="E90">
-        <v>-33.0314102076044</v>
+        <v>-30.26030039424097</v>
       </c>
       <c r="F90">
-        <v>0.2795655675232974</v>
+        <v>-1.480969472218312</v>
       </c>
       <c r="G90">
-        <v>-4.413182532064383</v>
+        <v>-4.28584085388824</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-3.151734692156714</v>
       </c>
       <c r="E91">
-        <v>-33.22375580708552</v>
+        <v>-31.46305378106602</v>
       </c>
       <c r="F91">
-        <v>-0.1853051068863543</v>
+        <v>-1.182207171255031</v>
       </c>
       <c r="G91">
-        <v>-4.536939657916926</v>
+        <v>-3.962750767759607</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-3.020515915025379</v>
       </c>
       <c r="E92">
-        <v>-34.270194779278</v>
+        <v>-32.82085692967523</v>
       </c>
       <c r="F92">
-        <v>0.4044113039014193</v>
+        <v>-1.293935709809822</v>
       </c>
       <c r="G92">
-        <v>-5.155571253248765</v>
+        <v>-3.941209514138332</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-2.876530856081118</v>
       </c>
       <c r="E93">
-        <v>-34.36599482830216</v>
+        <v>-33.78613799936923</v>
       </c>
       <c r="F93">
-        <v>-0.6653315912976259</v>
+        <v>-1.56750735805397</v>
       </c>
       <c r="G93">
-        <v>-4.852333268990957</v>
+        <v>-4.303549534449762</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-2.721141238846421</v>
       </c>
       <c r="E94">
-        <v>-38.11694064044744</v>
+        <v>-36.1464349911429</v>
       </c>
       <c r="F94">
-        <v>-0.3963756062218768</v>
+        <v>-1.41642474092698</v>
       </c>
       <c r="G94">
-        <v>-5.14151239362562</v>
+        <v>-4.108320664670901</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-2.559798923687543</v>
       </c>
       <c r="E95">
-        <v>-39.89763830239033</v>
+        <v>-37.95497162859611</v>
       </c>
       <c r="F95">
-        <v>-0.5741258551471919</v>
+        <v>-1.818226006389685</v>
       </c>
       <c r="G95">
-        <v>-5.35821985915557</v>
+        <v>-4.010699702919994</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-2.39699979931402</v>
       </c>
       <c r="E96">
-        <v>-41.99561223707084</v>
+        <v>-38.67482698147202</v>
       </c>
       <c r="F96">
-        <v>-0.8881375716286088</v>
+        <v>-1.906796705831814</v>
       </c>
       <c r="G96">
-        <v>-5.558064525371519</v>
+        <v>-4.745545982980651</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-2.236453601615015</v>
       </c>
       <c r="E97">
-        <v>-43.78799495907613</v>
+        <v>-41.06669045592005</v>
       </c>
       <c r="F97">
-        <v>-1.307651817265377</v>
+        <v>-1.959713643890049</v>
       </c>
       <c r="G97">
-        <v>-4.935383665178862</v>
+        <v>-4.832684805198238</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-2.082662643319528</v>
       </c>
       <c r="E98">
-        <v>-43.20416766011667</v>
+        <v>-42.40173192986354</v>
       </c>
       <c r="F98">
-        <v>-1.627714757624244</v>
+        <v>-2.373215598917298</v>
       </c>
       <c r="G98">
-        <v>-6.164086224328281</v>
+        <v>-5.400064873461933</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-1.936244411881703</v>
       </c>
       <c r="E99">
-        <v>-46.54150969266192</v>
+        <v>-44.39960931840436</v>
       </c>
       <c r="F99">
-        <v>-1.687792103512278</v>
+        <v>-2.354321366826844</v>
       </c>
       <c r="G99">
-        <v>-6.129794094124008</v>
+        <v>-5.161223515288525</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-1.798876938644784</v>
       </c>
       <c r="E100">
-        <v>-49.06706919286751</v>
+        <v>-46.78721990445577</v>
       </c>
       <c r="F100">
-        <v>-1.929164282442206</v>
+        <v>-2.345443753371042</v>
       </c>
       <c r="G100">
-        <v>-6.124301087504305</v>
+        <v>-5.53351569398128</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-1.66792191026105</v>
       </c>
       <c r="E101">
-        <v>-49.94668093426144</v>
+        <v>-48.19079455677308</v>
       </c>
       <c r="F101">
-        <v>-2.276952679772773</v>
+        <v>-2.553537100260903</v>
       </c>
       <c r="G101">
-        <v>-6.851529214848093</v>
+        <v>-5.974243320640887</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-1.53867952659464</v>
       </c>
       <c r="E102">
-        <v>-51.40744738312731</v>
+        <v>-50.33691874694799</v>
       </c>
       <c r="F102">
-        <v>-2.413436149792825</v>
+        <v>-2.674128341658247</v>
       </c>
       <c r="G102">
-        <v>-6.513174105095221</v>
+        <v>-5.99594121893763</v>
       </c>
     </row>
   </sheetData>
